--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/datas_remessas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD04C38-E0E0-4380-8CB2-8E22DDA2E1C8}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{869C961F-7640-4CBB-9B99-0C75C89211B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -193,13 +193,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -497,22 +500,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -580,169 +583,169 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7">
         <v>46146</v>
       </c>
-      <c r="E5" s="6">
-        <v>46156</v>
-      </c>
-      <c r="F5" s="1" t="str">
+      <c r="E5" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7">
         <v>46146</v>
       </c>
-      <c r="E6" s="6">
-        <v>46156</v>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="E6" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7">
         <v>46146</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="7">
         <v>46149</v>
       </c>
-      <c r="F7" s="1" t="str">
+      <c r="F7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7">
         <v>46146</v>
       </c>
-      <c r="E8" s="6">
-        <v>46156</v>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="E8" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7">
         <v>46146</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="7">
         <v>46149</v>
       </c>
-      <c r="F9" s="1" t="str">
+      <c r="F9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="7">
         <v>46146</v>
       </c>
-      <c r="E10" s="6">
-        <v>46156</v>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="E10" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7">
         <v>46146</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="7">
         <v>46149</v>
       </c>
-      <c r="F11" s="1" t="str">
+      <c r="F11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="7">
         <v>46146</v>
       </c>
-      <c r="E12" s="6">
-        <v>46156</v>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="E12" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>

--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{869C961F-7640-4CBB-9B99-0C75C89211B5}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE64007-3303-4136-B7F0-609B7B639BD6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
   <si>
     <t>Remessa</t>
   </si>
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -194,15 +194,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -583,169 +574,169 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
         <v>46146</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>46148</v>
       </c>
-      <c r="F5" s="6" t="str">
+      <c r="F5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3">
         <v>46146</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="3">
         <v>46148</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3">
         <v>46146</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>46149</v>
       </c>
-      <c r="F7" s="6" t="str">
+      <c r="F7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3">
         <v>46146</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="3">
         <v>46148</v>
       </c>
-      <c r="F8" s="6" t="str">
+      <c r="F8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3">
         <v>46146</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="3">
         <v>46149</v>
       </c>
-      <c r="F9" s="6" t="str">
+      <c r="F9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3">
         <v>46146</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="3">
         <v>46148</v>
       </c>
-      <c r="F10" s="6" t="str">
+      <c r="F10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3">
         <v>46146</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="3">
         <v>46149</v>
       </c>
-      <c r="F11" s="6" t="str">
+      <c r="F11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>46146</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="3">
         <v>46148</v>
       </c>
-      <c r="F12" s="6" t="str">
+      <c r="F12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Concluído</v>
       </c>
@@ -1393,12 +1384,12 @@
       <c r="D43" s="3">
         <v>46199</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>34</v>
+      <c r="E43" s="3">
+        <v>46212</v>
       </c>
       <c r="F43" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1414,12 +1405,12 @@
       <c r="D44" s="3">
         <v>46199</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>34</v>
+      <c r="E44" s="3">
+        <v>46212</v>
       </c>
       <c r="F44" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">

--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE64007-3303-4136-B7F0-609B7B639BD6}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A754ECAA-947E-4CBE-AFD7-BF57B402F9E7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">

--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A754ECAA-947E-4CBE-AFD7-BF57B402F9E7}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51863B17-2375-46C0-8018-2ECE62A74A5C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
   <si>
     <t>Remessa</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>019</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
         <v>46146</v>
       </c>
       <c r="F3" s="1" t="str">
-        <f t="shared" ref="F3:F49" si="0">IF(OR(ISBLANK(E3), NOT(ISNUMBER(DAY(E3)))), "Pendente", "Concluído")</f>
+        <f t="shared" ref="F3:F50" si="0">IF(OR(ISBLANK(E3), NOT(ISNUMBER(DAY(E3)))), "Pendente", "Concluído")</f>
         <v>Concluído</v>
       </c>
     </row>
@@ -1522,9 +1525,25 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="3">
+        <v>46213</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>

--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51863B17-2375-46C0-8018-2ECE62A74A5C}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{266EC63D-0033-45D8-BB27-7FF53EAF1D5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
   <si>
     <t>Remessa</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1369,12 +1372,12 @@
       <c r="D42" s="3">
         <v>46199</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>34</v>
+      <c r="E42" s="3">
+        <v>46220</v>
       </c>
       <c r="F42" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1453,12 +1456,12 @@
       <c r="D46" s="3">
         <v>46204</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>34</v>
+      <c r="E46" s="3">
+        <v>46213</v>
       </c>
       <c r="F46" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1474,12 +1477,12 @@
       <c r="D47" s="3">
         <v>46204</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>34</v>
+      <c r="E47" s="3">
+        <v>46213</v>
       </c>
       <c r="F47" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1495,12 +1498,12 @@
       <c r="D48" s="3">
         <v>46209</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>34</v>
+      <c r="E48" s="3">
+        <v>46220</v>
       </c>
       <c r="F48" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1516,12 +1519,12 @@
       <c r="D49" s="3">
         <v>46209</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>34</v>
+      <c r="E49" s="3">
+        <v>46223</v>
       </c>
       <c r="F49" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,18 +1540,55 @@
       <c r="D50" s="3">
         <v>46213</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>34</v>
+      <c r="E50" s="3">
+        <v>46227</v>
       </c>
       <c r="F50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Pendente</v>
+        <f>IF(OR(ISBLANK(E50), NOT(ISNUMBER(DAY(E50)))), "Pendente", "Concluído")</f>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="3">
+        <v>46216</v>
+      </c>
+      <c r="E51" s="3">
+        <v>46230</v>
+      </c>
+      <c r="F51" s="1" t="str">
+        <f t="shared" ref="F51:F52" si="1">IF(OR(ISBLANK(E51), NOT(ISNUMBER(DAY(E51)))), "Pendente", "Concluído")</f>
+        <v>Concluído</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="3">
+        <v>46216</v>
+      </c>
+      <c r="E52" s="3">
+        <v>46230</v>
+      </c>
+      <c r="F52" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Concluído</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datas_remessas.xlsx
+++ b/datas_remessas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{266EC63D-0033-45D8-BB27-7FF53EAF1D5B}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="11_F25DC773A252ABDACC10489B791D7F6E5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84621AE-691A-4F8F-821D-73A54B598E4C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1275" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="38">
   <si>
     <t>Remessa</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -557,7 +560,7 @@
         <v>46146</v>
       </c>
       <c r="F3" s="1" t="str">
-        <f t="shared" ref="F3:F50" si="0">IF(OR(ISBLANK(E3), NOT(ISNUMBER(DAY(E3)))), "Pendente", "Concluído")</f>
+        <f t="shared" ref="F3:F49" si="0">IF(OR(ISBLANK(E3), NOT(ISNUMBER(DAY(E3)))), "Pendente", "Concluído")</f>
         <v>Concluído</v>
       </c>
     </row>
@@ -1565,7 +1568,7 @@
         <v>46230</v>
       </c>
       <c r="F51" s="1" t="str">
-        <f t="shared" ref="F51:F52" si="1">IF(OR(ISBLANK(E51), NOT(ISNUMBER(DAY(E51)))), "Pendente", "Concluído")</f>
+        <f t="shared" ref="F51:F54" si="1">IF(OR(ISBLANK(E51), NOT(ISNUMBER(DAY(E51)))), "Pendente", "Concluído")</f>
         <v>Concluído</v>
       </c>
     </row>
@@ -1588,6 +1591,48 @@
       <c r="F52" s="1" t="str">
         <f t="shared" si="1"/>
         <v>Concluído</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="3">
+        <v>46220</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pendente</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="3">
+        <v>46220</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pendente</v>
       </c>
     </row>
   </sheetData>
